--- a/src/assets/templates/Template-uploadUser.xlsx
+++ b/src/assets/templates/Template-uploadUser.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rawee\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DF50F144-4E0C-421E-9FDB-A27EA8D7C9A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5DBB1F30-D88C-400D-90AE-C646268085F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{847E8D8F-B098-457A-B592-8A4FFAC65196}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="44">
   <si>
     <t>หน้าที่</t>
   </si>
@@ -108,9 +108,6 @@
     <t>2.) รหัสอาจารย์</t>
   </si>
   <si>
-    <t>2.) คำนำหน้า</t>
-  </si>
-  <si>
     <t>3.) คำนำหน้า</t>
   </si>
   <si>
@@ -135,25 +132,43 @@
     <t>1.) รหัสอาจารย์</t>
   </si>
   <si>
-    <t>3.) ชื่อ</t>
-  </si>
-  <si>
-    <t>4.) นามสกุล</t>
-  </si>
-  <si>
     <t>วิธีเพิ่มข้อมูล</t>
   </si>
   <si>
     <t>ต้องกดเลือกข้อมูลจาก Drop-down-list ในคอลัมน์ชื่อดังนี้</t>
   </si>
   <si>
-    <t>กรอกข้อมูลคอลัมน์ดังนี้</t>
-  </si>
-  <si>
     <t>6.) อีเมล</t>
   </si>
   <si>
-    <t>5.) อีเมล</t>
+    <t>2.) ชื่อ</t>
+  </si>
+  <si>
+    <t>กรอกข้อมูลในคอลัมน์ดังนี้</t>
+  </si>
+  <si>
+    <t>3.) นามสกุล</t>
+  </si>
+  <si>
+    <t>4.) อีเมล</t>
+  </si>
+  <si>
+    <t>S4044</t>
+  </si>
+  <si>
+    <t>S4045</t>
+  </si>
+  <si>
+    <t>S4046</t>
+  </si>
+  <si>
+    <t>example3@si.ku.th</t>
+  </si>
+  <si>
+    <t>example4@si.ku.th</t>
+  </si>
+  <si>
+    <t>example5@si.ku.th</t>
   </si>
 </sst>
 </file>
@@ -216,7 +231,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -229,8 +244,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -238,12 +265,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -252,6 +294,8 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -292,8 +336,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2606C8FD-2CD3-4B54-9902-217BBFC94065}" name="Table1" displayName="Table1" ref="A1:F3" totalsRowShown="0" headerRowDxfId="1" tableBorderDxfId="0">
-  <autoFilter ref="A1:F3" xr:uid="{2606C8FD-2CD3-4B54-9902-217BBFC94065}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2606C8FD-2CD3-4B54-9902-217BBFC94065}" name="Table1" displayName="Table1" ref="A1:F6" totalsRowShown="0" headerRowDxfId="1" tableBorderDxfId="0">
+  <autoFilter ref="A1:F6" xr:uid="{2606C8FD-2CD3-4B54-9902-217BBFC94065}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{2C616A14-D21E-4F7C-B1B9-85C5ABECB5AE}" name="หน้าที่"/>
     <tableColumn id="2" xr3:uid="{7ABCE258-A8C2-4717-A47A-AA544AE298A2}" name="รหัสอาจารย์"/>
@@ -623,7 +667,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12088307-A943-4313-8FB9-FFB1D7F99E1E}">
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.625" customWidth="1"/>
@@ -660,24 +704,24 @@
         <v>5</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
         <v>20</v>
@@ -689,18 +733,18 @@
         <v>7</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="J2" t="s">
         <v>21</v>
       </c>
       <c r="K2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
@@ -721,57 +765,106 @@
         <v>22</v>
       </c>
       <c r="K3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="J4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="J5" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="J5" t="s">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="J6" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="J6" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="J7" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15" x14ac:dyDescent="0.2">
       <c r="J9" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="J10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="J11" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="J12" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="J13" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="J14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -779,25 +872,30 @@
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1" xr:uid="{8D35C347-ED97-486A-A43A-2E82E456686D}"/>
     <hyperlink ref="F3" r:id="rId2" xr:uid="{9CA7E69A-00E6-4146-8AF3-2D3A00692D2E}"/>
+    <hyperlink ref="F4:F6" r:id="rId3" display="example2@si.ku.th" xr:uid="{EB48F875-A1E8-4CD1-A69F-F4B2EC4A4DA2}"/>
+    <hyperlink ref="F4" r:id="rId4" xr:uid="{4DEFA980-EE19-4E36-BC85-F45805F2AC7E}"/>
+    <hyperlink ref="F5" r:id="rId5" xr:uid="{A541B298-2DBE-4646-85BC-86AA83616636}"/>
+    <hyperlink ref="F6" r:id="rId6" xr:uid="{ED0E5D90-7E05-41EB-A55F-880B0DA40D2A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId7"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId8"/>
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{8E6F3FD4-5DF9-4675-9468-1A291F434092}">
           <x14:formula1>
-            <xm:f>'ข้อมูล Drop-down-list'!$I$1:$I$2</xm:f>
+            <xm:f>'ข้อมูล Drop-down-list'!$B$1:$B$2</xm:f>
           </x14:formula1>
-          <xm:sqref>A2:A3</xm:sqref>
+          <xm:sqref>A2:A6</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{088D7054-A4BC-4D16-9F32-E509A40B665C}">
           <x14:formula1>
-            <xm:f>'ข้อมูล Drop-down-list'!$H$1:$H$8</xm:f>
+            <xm:f>'ข้อมูล Drop-down-list'!$A$1:$A$8</xm:f>
           </x14:formula1>
-          <xm:sqref>C2:C3</xm:sqref>
+          <xm:sqref>C2:C6</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -807,71 +905,57 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2EE03E6-9BA4-4702-822B-B11510468818}">
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
-        <v>9</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" t="s">
-        <v>10</v>
-      </c>
-      <c r="I2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="H3" t="s">
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" s="8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="H4" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="H5" t="s">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="E6" s="1"/>
-      <c r="H6" t="s">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" s="8" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="H7" t="s">
+      <c r="D6" s="1"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" s="8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="H8" t="s">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" s="8" t="s">
         <v>16</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1" xr:uid="{89E4D2DD-893A-4B2E-92F2-6E9AD5150C10}">
-      <formula1>$I$1:$I$2</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2" xr:uid="{FA216E57-2BFA-441F-BFD3-9E6A50744BB8}">
-      <formula1>$H$1:$H$8</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/src/assets/templates/Template-uploadUser.xlsx
+++ b/src/assets/templates/Template-uploadUser.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rawee\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5DBB1F30-D88C-400D-90AE-C646268085F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FA2C54E-E898-4C20-917A-97531B8817E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{847E8D8F-B098-457A-B592-8A4FFAC65196}"/>
   </bookViews>
@@ -60,9 +60,6 @@
     <t>อาจารย์</t>
   </si>
   <si>
-    <t>example1@si.ku.th</t>
-  </si>
-  <si>
     <t>ผู้ดูแลระบบ</t>
   </si>
   <si>
@@ -90,9 +87,6 @@
     <t>รศ.ดร.</t>
   </si>
   <si>
-    <t>example2@si.ku.th</t>
-  </si>
-  <si>
     <t>S4042</t>
   </si>
   <si>
@@ -162,13 +156,19 @@
     <t>S4046</t>
   </si>
   <si>
-    <t>example3@si.ku.th</t>
-  </si>
-  <si>
-    <t>example4@si.ku.th</t>
-  </si>
-  <si>
-    <t>example5@si.ku.th</t>
+    <t>example1@ku.th</t>
+  </si>
+  <si>
+    <t>example2@ku.th</t>
+  </si>
+  <si>
+    <t>example3@ku.th</t>
+  </si>
+  <si>
+    <t>example4@ku.th</t>
+  </si>
+  <si>
+    <t>example5@ku.th</t>
   </si>
 </sst>
 </file>
@@ -704,42 +704,42 @@
         <v>5</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
         <v>18</v>
       </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>20</v>
-      </c>
       <c r="E2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -747,25 +747,25 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="J3" t="s">
         <v>20</v>
       </c>
-      <c r="E3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="J3" t="s">
-        <v>22</v>
-      </c>
       <c r="K3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
@@ -773,22 +773,22 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>41</v>
       </c>
       <c r="J4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
@@ -796,22 +796,22 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>42</v>
       </c>
       <c r="J5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
@@ -819,52 +819,52 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>43</v>
       </c>
       <c r="J6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="J7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15" x14ac:dyDescent="0.2">
       <c r="J9" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="J10" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="J11" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="J12" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="J13" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -910,15 +910,15 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B2" s="9" t="s">
         <v>6</v>
@@ -926,33 +926,33 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D6" s="1"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -961,20 +961,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="5f57a6f6-9a89-4746-97fb-1b0e2ec9618d" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="5f57a6f6-9a89-4746-97fb-1b0e2ec9618d" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1205,14 +1205,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA26BF37-D634-40EC-9C53-90EC46C689A8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80E88AF7-5A9D-4DEB-9874-E9BF15675A46}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -1225,6 +1217,14 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA26BF37-D634-40EC-9C53-90EC46C689A8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
